--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844124</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70816998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70819992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74769827</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74411391</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70819885</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74843778</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74414984</t>
         </is>
       </c>
     </row>
@@ -1683,6 +1728,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70820520</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74782286</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1898,8 +1953,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70819851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70816998</v>
+        <v>136274561</v>
       </c>
       <c r="B3" t="n">
-        <v>57132</v>
+        <v>96599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,48 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hagsjölid, Hästspångsberget, Bostorp, Sm</t>
+          <t>Krokarp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567991</v>
+        <v>569374</v>
       </c>
       <c r="R3" t="n">
-        <v>6376497</v>
+        <v>6375748</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,27 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sett och hört</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,27 +886,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Elin Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Backman, Naja Sköldén</t>
+          <t>Elin Jonsson, Julia Odéhn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70816998</t>
+          <t>https://artportalen.se/Sighting/136274561</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70819992</v>
+        <v>136274569</v>
       </c>
       <c r="B4" t="n">
-        <v>58815</v>
+        <v>96599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,54 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagsjön nedom Hagsjölid, Sm</t>
+          <t>Krokarp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568050</v>
+        <v>569367</v>
       </c>
       <c r="R4" t="n">
-        <v>6376679</v>
+        <v>6375729</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,22 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,27 +988,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Elin Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Backman, Naja Sköldén</t>
+          <t>Elin Jonsson, Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70819992</t>
+          <t>https://artportalen.se/Sighting/136274569</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74769827</v>
+        <v>136274571</v>
       </c>
       <c r="B5" t="n">
-        <v>99153</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,37 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>L3 Mjöshultesjöns SO-spets 150 m SSV, Sm</t>
+          <t>Krokarp, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566469</v>
+        <v>569396</v>
       </c>
       <c r="R5" t="n">
-        <v>6376033</v>
+        <v>6375744</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,17 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6G5d 2432. SOM: Platanthera bifolia. LEG: Sören Mjösberg</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,78 +1086,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>F.d. betesmark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Elin Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Elin Jonsson, Frida Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74769827</t>
+          <t>https://artportalen.se/Sighting/136274571</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74411391</v>
+        <v>136274587</v>
       </c>
       <c r="B6" t="n">
-        <v>106812</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>L6 Mjöshultesjöns S-spets 1400 m ONO t O, Sm</t>
+          <t>Krokarp, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567962</v>
+        <v>569458</v>
       </c>
       <c r="R6" t="n">
-        <v>6376551</v>
+        <v>6375575</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,17 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6G5d 2947. SOM: Fraxinus excelsior. LEG: Sören Mjösberg</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,85 +1188,69 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>F.d. tomt</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Elin Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Elin Jonsson, Frida Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74411391</t>
+          <t>https://artportalen.se/Sighting/136274587</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70819885</v>
+        <v>136274562</v>
       </c>
       <c r="B7" t="n">
-        <v>106156</v>
+        <v>102422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221141</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hagsjölid, Hästspångsberget, Bostorp, Sm</t>
+          <t>Krokarp, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567991</v>
+        <v>569373</v>
       </c>
       <c r="R7" t="n">
-        <v>6376497</v>
+        <v>6375741</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,65 +1294,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Backman</t>
+          <t>Elin Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Backman, Naja Sköldén</t>
+          <t>Elin Jonsson, Julia Odéhn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70819885</t>
+          <t>https://artportalen.se/Sighting/136274562</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74843778</v>
+        <v>136274573</v>
       </c>
       <c r="B8" t="n">
-        <v>106155</v>
+        <v>102422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>L2 Holmsjöns N-spets 550 m VNV t V, Sm</t>
+          <t>Krokarp, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567674</v>
+        <v>569372</v>
       </c>
       <c r="R8" t="n">
-        <v>6375548</v>
+        <v>6375760</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1464,17 +1376,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6G5d 1944. SOM: Primula veris. LEG: Sören Mjösberg</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,57 +1392,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>F.d. betesmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Elin Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Elin Jonsson, Frida Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74843778</t>
+          <t>https://artportalen.se/Sighting/136274573</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74414984</v>
+        <v>136274586</v>
       </c>
       <c r="B9" t="n">
-        <v>107294</v>
+        <v>99102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221647</v>
+        <v>223049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1546,17 +1444,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mjöshult 1200 m OSO, Sm</t>
+          <t>Krokarp, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567962</v>
+        <v>569458</v>
       </c>
       <c r="R9" t="n">
-        <v>6376551</v>
+        <v>6375577</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,17 +1478,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6G5d 2947. SOM: Galeopsis ladanum. LEG: Sören Mjösberg</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,40 +1494,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Vid torpruin i skog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Elin Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Elin Jonsson, Frida Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74414984</t>
+          <t>https://artportalen.se/Sighting/136274586</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70820520</v>
+        <v>70816998</v>
       </c>
       <c r="B10" t="n">
-        <v>97986</v>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,37 +1526,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hagsjön nedom Hagsjölid, Sm</t>
+          <t>Hagsjölid, Hästspångsberget, Bostorp, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568050</v>
+        <v>567991</v>
       </c>
       <c r="R10" t="n">
-        <v>6376679</v>
+        <v>6376497</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1702,9 +1594,24 @@
           <t>2018-04-22</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sett och hört</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,51 +1637,68 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70820520</t>
+          <t>https://artportalen.se/Sighting/70816998</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74782286</v>
+        <v>70819992</v>
       </c>
       <c r="B11" t="n">
-        <v>102559</v>
+        <v>58815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222133</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>L2 Holmsjöns N-spets 550 m VNV t V, Sm</t>
+          <t>Hagsjön nedom Hagsjölid, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567674</v>
+        <v>568050</v>
       </c>
       <c r="R11" t="n">
-        <v>6375548</v>
+        <v>6376679</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1801,17 +1725,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6G5d 1944. SOM: Polygala vulgaris. LEG: Sören Mjösberg</t>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,40 +1751,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Torrbacke</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Per Backman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Per Backman, Naja Sköldén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74782286</t>
+          <t>https://artportalen.se/Sighting/70819992</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>70819851</v>
+        <v>74769827</v>
       </c>
       <c r="B12" t="n">
-        <v>101326</v>
+        <v>99153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,41 +1783,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hagsjölid, Hästspångsberget, Bostorp, Sm</t>
+          <t>L3 Mjöshultesjöns SO-spets 150 m SSV, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567991</v>
+        <v>566469</v>
       </c>
       <c r="R12" t="n">
-        <v>6376497</v>
+        <v>6376033</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1924,12 +1837,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G5d 2432. SOM: Platanthera bifolia. LEG: Sören Mjösberg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,22 +1858,5053 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>F.d. betesmark</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74769827</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>74411391</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L6 Mjöshultesjöns S-spets 1400 m ONO t O, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567962</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6376551</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G5d 2947. SOM: Fraxinus excelsior. LEG: Sören Mjösberg</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>F.d. tomt</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74411391</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>70819885</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hagsjölid, Hästspångsberget, Bostorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567991</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6376497</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Per Backman</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Per Backman, Naja Sköldén</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70819885</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74843778</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L2 Holmsjöns N-spets 550 m VNV t V, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567674</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6375548</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G5d 1944. SOM: Primula veris. LEG: Sören Mjösberg</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>F.d. betesmark</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74843778</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74414984</v>
+      </c>
+      <c r="B16" t="n">
+        <v>107294</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221647</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mjukdån</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Galeopsis ladanum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mjöshult 1200 m OSO, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>567962</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6376551</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1986-12-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G5d 2947. SOM: Galeopsis ladanum. LEG: Sören Mjösberg</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Vid torpruin i skog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74414984</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>70820520</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hagsjön nedom Hagsjölid, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>568050</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6376679</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Backman, Naja Sköldén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70820520</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>74782286</v>
+      </c>
+      <c r="B18" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L2 Holmsjöns N-spets 550 m VNV t V, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567674</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6375548</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G5d 1944. SOM: Polygala vulgaris. LEG: Sören Mjösberg</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Torrbacke</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74782286</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>70819851</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hagsjölid, Hästspångsberget, Bostorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567991</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6376497</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Per Backman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Per Backman, Naja Sköldén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/70819851</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136274678</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96881</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>570465</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6375985</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274678</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136274680</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96881</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570435</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6376001</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274680</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136274673</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56923</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>570471</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6375979</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274673</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136274681</v>
+      </c>
+      <c r="B23" t="n">
+        <v>43391</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>570450</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6375704</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274681</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136274674</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98158</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>570222</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6375520</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274674</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136274683</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98158</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>570348</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6375740</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274683</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136274684</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98158</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570277</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6375728</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274684</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136274766</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101506</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>569993</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6375348</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Frida Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274766</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136274632</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96404</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>570809</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6375694</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274632</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136274579</v>
+      </c>
+      <c r="B29" t="n">
+        <v>75535</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>571442</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6375002</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274579</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136274660</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>570652</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6375553</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274660</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136274567</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>571440</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6375126</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274567</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136274570</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>571451</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6375041</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274570</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136274575</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>571467</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6374993</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Vittoppad spillning i riklig mängd i kringområdet, kan indikera spelplats</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274575</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136274589</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>571378</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6375485</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274589</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136274596</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>571541</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6375201</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274596</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136274600</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>571520</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6375334</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274600</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136274601</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>571415</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6375335</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Vittoppad spillning i riklig mängd i kringområdet, kan indikera spelplats</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274601</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136274602</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>571459</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6375337</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Vittoppad spillning i riklig mängd i kringområdet, kan indikera spelplats</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274602</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136274603</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>571559</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6375372</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274603</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136274604</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>571544</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6375556</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Vittoppad spillning i riklig mängd i kringområdet, kan indikera spelplats</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274604</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136274578</v>
+      </c>
+      <c r="B41" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>571428</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6375011</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274578</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136274580</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>571458</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6374998</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274580</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136274582</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>571446</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6375015</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274582</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136274635</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43391</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>570727</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6375517</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274635</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136274620</v>
+      </c>
+      <c r="B45" t="n">
+        <v>56714</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>571476</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6375768</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274620</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136274598</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98158</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>571645</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6375234</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274598</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136274628</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98158</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>571051</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6376059</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274628</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136274668</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98158</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>570527</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6375977</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274668</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136274606</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98161</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>571489</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6375507</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274606</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136274590</v>
+      </c>
+      <c r="B50" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>571382</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6375311</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274590</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136274592</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>571350</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6375241</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274592</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136274621</v>
+      </c>
+      <c r="B52" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>571599</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6375493</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274621</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136274633</v>
+      </c>
+      <c r="B53" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>570807</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6375679</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274633</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136274638</v>
+      </c>
+      <c r="B54" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>570812</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6375726</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274638</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136274647</v>
+      </c>
+      <c r="B55" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>570955</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6375935</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274647</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136274664</v>
+      </c>
+      <c r="B56" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>570782</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6375541</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274664</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136274667</v>
+      </c>
+      <c r="B57" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>570764</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6375534</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274667</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136274670</v>
+      </c>
+      <c r="B58" t="n">
+        <v>102744</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>570728</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6375476</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274670</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136274565</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101506</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>571118</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6375585</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274565</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136274597</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101506</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Krokarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>571445</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6375269</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Elin Jonsson, Sofia Asplund</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136274597</t>
         </is>
       </c>
     </row>
@@ -1972,6 +6921,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136274561</v>
       </c>
       <c r="B3" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136274569</v>
       </c>
       <c r="B4" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136274571</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136274587</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136274562</v>
       </c>
       <c r="B7" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136274573</v>
       </c>
       <c r="B8" t="n">
-        <v>102422</v>
+        <v>102428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136274586</v>
       </c>
       <c r="B9" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136274678</v>
       </c>
       <c r="B20" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136274680</v>
       </c>
       <c r="B21" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136274673</v>
       </c>
       <c r="B22" t="n">
-        <v>56923</v>
+        <v>56927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136274674</v>
       </c>
       <c r="B24" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>136274683</v>
       </c>
       <c r="B25" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136274684</v>
       </c>
       <c r="B26" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136274766</v>
       </c>
       <c r="B27" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136274632</v>
       </c>
       <c r="B28" t="n">
-        <v>96404</v>
+        <v>96410</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136274579</v>
       </c>
       <c r="B29" t="n">
-        <v>75535</v>
+        <v>75539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136274660</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>136274567</v>
       </c>
       <c r="B31" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136274570</v>
       </c>
       <c r="B32" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>136274575</v>
       </c>
       <c r="B33" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>136274589</v>
       </c>
       <c r="B34" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>136274596</v>
       </c>
       <c r="B35" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>136274600</v>
       </c>
       <c r="B36" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>136274601</v>
       </c>
       <c r="B37" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136274602</v>
       </c>
       <c r="B38" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>136274603</v>
       </c>
       <c r="B39" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>136274604</v>
       </c>
       <c r="B40" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>136274620</v>
       </c>
       <c r="B45" t="n">
-        <v>56714</v>
+        <v>56718</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136274598</v>
       </c>
       <c r="B46" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136274628</v>
       </c>
       <c r="B47" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136274668</v>
       </c>
       <c r="B48" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>136274606</v>
       </c>
       <c r="B49" t="n">
-        <v>98161</v>
+        <v>98167</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>136274590</v>
       </c>
       <c r="B50" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>136274592</v>
       </c>
       <c r="B51" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>136274621</v>
       </c>
       <c r="B52" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136274633</v>
       </c>
       <c r="B53" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>136274638</v>
       </c>
       <c r="B54" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136274647</v>
       </c>
       <c r="B55" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136274664</v>
       </c>
       <c r="B56" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>136274667</v>
       </c>
       <c r="B57" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136274670</v>
       </c>
       <c r="B58" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>136274565</v>
       </c>
       <c r="B59" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136274597</v>
       </c>
       <c r="B60" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/S 222-2023 artfynd.xlsx
+++ b/artfynd/S 222-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136274561</v>
       </c>
       <c r="B3" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>136274569</v>
       </c>
       <c r="B4" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>136274571</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>136274587</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136274562</v>
       </c>
       <c r="B7" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>136274573</v>
       </c>
       <c r="B8" t="n">
-        <v>102428</v>
+        <v>102429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136274586</v>
       </c>
       <c r="B9" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136274678</v>
       </c>
       <c r="B20" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>136274680</v>
       </c>
       <c r="B21" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136274673</v>
       </c>
       <c r="B22" t="n">
-        <v>56927</v>
+        <v>56928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>136274674</v>
       </c>
       <c r="B24" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>136274683</v>
       </c>
       <c r="B25" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136274684</v>
       </c>
       <c r="B26" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136274766</v>
       </c>
       <c r="B27" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136274632</v>
       </c>
       <c r="B28" t="n">
-        <v>96410</v>
+        <v>96411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136274579</v>
       </c>
       <c r="B29" t="n">
-        <v>75539</v>
+        <v>75540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>136274660</v>
       </c>
       <c r="B30" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>136274567</v>
       </c>
       <c r="B31" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136274570</v>
       </c>
       <c r="B32" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>136274575</v>
       </c>
       <c r="B33" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>136274589</v>
       </c>
       <c r="B34" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>136274596</v>
       </c>
       <c r="B35" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>136274600</v>
       </c>
       <c r="B36" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>136274601</v>
       </c>
       <c r="B37" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>136274602</v>
       </c>
       <c r="B38" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>136274603</v>
       </c>
       <c r="B39" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>136274604</v>
       </c>
       <c r="B40" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>136274620</v>
       </c>
       <c r="B45" t="n">
-        <v>56718</v>
+        <v>56719</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>136274598</v>
       </c>
       <c r="B46" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136274628</v>
       </c>
       <c r="B47" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136274668</v>
       </c>
       <c r="B48" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>136274606</v>
       </c>
       <c r="B49" t="n">
-        <v>98167</v>
+        <v>98168</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>136274590</v>
       </c>
       <c r="B50" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>136274592</v>
       </c>
       <c r="B51" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>136274621</v>
       </c>
       <c r="B52" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136274633</v>
       </c>
       <c r="B53" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>136274638</v>
       </c>
       <c r="B54" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>136274647</v>
       </c>
       <c r="B55" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136274664</v>
       </c>
       <c r="B56" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>136274667</v>
       </c>
       <c r="B57" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136274670</v>
       </c>
       <c r="B58" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>136274565</v>
       </c>
       <c r="B59" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136274597</v>
       </c>
       <c r="B60" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
